--- a/ExcelTool/LubanTools/DataTables/Datas/SprayPaintGameData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/SprayPaintGameData.xlsx
@@ -1,29 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\text\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="28800" windowHeight="14360" tabRatio="500"/>
+    <workbookView windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1785316232" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1785316232" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1785316232" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1785316232"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -91,51 +100,173 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="49" formatCode="@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="2">
-    <font>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785316232" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1785316232" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,78 +275,509 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1785316232" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785316232"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="none">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="none">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1785316232"/>
-        </ext>
-      </extLst>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="常规 2" xfId="1"/>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <tableStyles count="0"/>
   <extLst>
-    <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1785316232" count="1">
-        <pm:charStyle name="普通" fontId="0" Id="1"/>
-      </pm:charStyles>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -445,9 +1007,6 @@
     <a:spDef>
       <a:spPr/>
       <a:bodyPr>
-        <a:prstTxWarp prst="textNoShape">
-          <a:avLst/>
-        </a:prstTxWarp>
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -471,41 +1030,41 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F200"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="11.163793" customWidth="1"/>
-    <col min="4" max="4" width="31.750000" customWidth="1" style="2"/>
-    <col min="5" max="5" width="78.577586" customWidth="1"/>
-    <col min="6" max="6" width="54.577586" customWidth="1"/>
-    <col min="7" max="7" width="26.577586" customWidth="1"/>
-    <col min="8" max="8" width="22.577586" customWidth="1"/>
-    <col min="9" max="9" width="14.577586" customWidth="1"/>
+    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
+    <col min="4" max="4" width="87.8333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="78.575" customWidth="1"/>
+    <col min="6" max="6" width="54.575" customWidth="1"/>
+    <col min="7" max="7" width="26.575" customWidth="1"/>
+    <col min="8" max="8" width="22.575" customWidth="1"/>
+    <col min="9" max="9" width="14.575" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -513,19 +1072,19 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -533,115 +1092,199 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
-      <c r="B4" t="n">
+    <row r="4" spans="1:6">
+      <c r="B4">
         <v>10001</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
-      <c r="B5" t="n">
+    <row r="5" spans="1:6">
+      <c r="B5">
         <v>10002</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
-      <c r="B6" t="n">
+    <row r="6" spans="1:6">
+      <c r="B6">
         <v>10003</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
-      <c r="B7" t="n">
+    <row r="7" spans="1:6">
+      <c r="B7">
         <v>10004</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="4:4">
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="4:4">
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="4:4">
-      <c r="D10"/>
-    </row>
-    <row r="11" spans="4:4">
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="4:4">
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="4:4">
-      <c r="D13"/>
-    </row>
-    <row r="14" spans="4:4">
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>10005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>10006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10">
+        <v>10007</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11">
+        <v>10008</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12">
+        <v>10009</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13">
+        <v>10010</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="D14"/>
     </row>
-    <row r="15" spans="4:4">
+    <row r="15" spans="1:6">
       <c r="D15"/>
     </row>
-    <row r="16" spans="4:4">
+    <row r="16" spans="1:6">
       <c r="D16"/>
     </row>
     <row r="17" spans="4:4">
@@ -1197,32 +1840,8 @@
       <c r="D200"/>
     </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1785316232" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1785316232" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1785316232" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785316232" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1785316232" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
-  <extLst>
-    <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1785316232" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
-        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
-        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
-      </pm:sheetPrefs>
-    </ext>
-  </extLst>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>